--- a/Escala de Trabalho.xlsx
+++ b/Escala de Trabalho.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spotpromo.sharepoint.com/sites/bko.lbasaia/Documentos Compartilhados/PMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1097" documentId="8_{C9589A86-DEFA-4536-898C-3C99E4F500E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B16963E-CA4F-44F9-BD87-5400652B9100}"/>
+  <xr:revisionPtr revIDLastSave="1104" documentId="8_{C9589A86-DEFA-4536-898C-3C99E4F500E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF43C6DE-7E1A-4FBB-BE34-F29F959D9FD9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8597F27F-AEEC-4BA4-9237-ED3EB9E49D86}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="19">
   <si>
     <t>GUSTAVO</t>
   </si>
@@ -94,6 +94,9 @@
   <si>
     <t>SPOT LESTE</t>
   </si>
+  <si>
+    <t>ATESTADO</t>
+  </si>
 </sst>
 </file>
 
@@ -132,7 +135,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +157,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -185,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -193,11 +202,12 @@
     <xf numFmtId="16" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="279">
+  <dxfs count="245">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -235,6 +245,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -256,36 +276,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -352,6 +342,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -397,46 +407,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -454,21 +424,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -484,21 +454,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -520,6 +490,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -596,31 +606,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -652,46 +642,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -728,6 +678,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -804,31 +784,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -850,21 +820,31 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -946,21 +926,31 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -982,6 +972,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1058,6 +1058,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1114,6 +1124,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1236,16 +1256,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1312,6 +1322,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1322,11 +1342,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1378,6 +1398,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1444,16 +1474,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1509,46 +1529,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -1566,6 +1546,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1622,26 +1622,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1652,21 +1632,51 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1688,21 +1698,31 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1718,21 +1738,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1754,26 +1764,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1784,11 +1774,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1820,31 +1810,31 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1870,11 +1860,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1925,26 +1925,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -1962,21 +1942,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1992,21 +1972,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2028,31 +2008,41 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2084,11 +2074,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2104,21 +2094,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2140,11 +2130,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2160,21 +2160,61 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2205,36 +2245,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -2252,31 +2262,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2292,21 +2292,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2328,11 +2328,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2353,26 +2363,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2394,21 +2384,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2419,6 +2409,46 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2470,41 +2500,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2536,6 +2536,56 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2546,21 +2596,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2602,31 +2642,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2648,21 +2668,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2678,21 +2698,51 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2714,11 +2764,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2734,21 +2794,42 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2770,31 +2851,31 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2805,459 +2886,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3605,6 +3233,7 @@
     <col min="12" max="12" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="1.77734375" customWidth="1"/>
+    <col min="16" max="17" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="1.44140625" customWidth="1"/>
     <col min="26" max="26" width="7.21875" bestFit="1" customWidth="1"/>
@@ -5367,11 +4996,11 @@
       <c r="M50" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="P50" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q50" s="3" t="s">
-        <v>9</v>
+      <c r="P50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q50" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="R50" s="3" t="s">
         <v>16</v>
@@ -5380,7 +5009,7 @@
         <v>9</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W50" s="3" t="s">
         <v>10</v>
@@ -7064,972 +6693,858 @@
     </row>
   </sheetData>
   <autoFilter ref="A16:A24" xr:uid="{FA93638E-3964-4B9F-B2A5-0DADAAE5D49F}"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="cellIs" dxfId="244" priority="628" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="243" priority="627" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="242" priority="629" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:F12">
+    <cfRule type="cellIs" dxfId="241" priority="621" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="240" priority="620" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="278" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="239" priority="75" operator="equal">
+      <formula>"CAMPO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="238" priority="68" operator="equal">
+      <formula>"PLATINA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="237" priority="67" operator="equal">
       <formula>"SPOT LESTE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="277" priority="68" operator="equal">
-      <formula>"PLATINA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="276" priority="75" operator="equal">
-      <formula>"CAMPO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="275" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="236" priority="82" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="cellIs" dxfId="274" priority="627" operator="equal">
+  <conditionalFormatting sqref="B50">
+    <cfRule type="cellIs" dxfId="235" priority="74" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="234" priority="73" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="233" priority="72" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="273" priority="628" operator="equal">
+    <cfRule type="cellIs" dxfId="232" priority="71" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="231" priority="70" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="230" priority="69" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:E47">
+    <cfRule type="cellIs" dxfId="229" priority="422" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:F12">
+    <cfRule type="cellIs" dxfId="228" priority="623" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="272" priority="629" operator="equal">
+    <cfRule type="cellIs" dxfId="227" priority="622" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="226" priority="624" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A12">
-    <cfRule type="cellIs" dxfId="271" priority="625" operator="equal">
+  <conditionalFormatting sqref="B26:F43">
+    <cfRule type="cellIs" dxfId="225" priority="461" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="224" priority="460" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="223" priority="459" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="222" priority="458" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="270" priority="626" operator="equal">
-      <formula>"FÉRIAS"</formula>
+    <cfRule type="cellIs" dxfId="221" priority="462" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:F34">
-    <cfRule type="cellIs" dxfId="269" priority="613" operator="equal">
+    <cfRule type="cellIs" dxfId="220" priority="613" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:F12">
-    <cfRule type="cellIs" dxfId="268" priority="620" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="267" priority="621" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="266" priority="622" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="265" priority="623" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="264" priority="624" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
-    <cfRule type="cellIs" dxfId="263" priority="69" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="262" priority="70" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="261" priority="71" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="260" priority="72" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="259" priority="73" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="258" priority="74" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47:E47">
-    <cfRule type="cellIs" dxfId="257" priority="422" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26:F34">
-    <cfRule type="cellIs" dxfId="256" priority="615" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="255" priority="616" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="254" priority="617" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="253" priority="618" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="252" priority="619" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:F43">
-    <cfRule type="cellIs" dxfId="251" priority="458" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="250" priority="459" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="249" priority="460" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="248" priority="461" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="247" priority="462" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36:F43">
-    <cfRule type="cellIs" dxfId="246" priority="457" operator="equal">
+    <cfRule type="cellIs" dxfId="219" priority="457" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:F46 B47:E47">
-    <cfRule type="cellIs" dxfId="245" priority="423" operator="equal">
+    <cfRule type="cellIs" dxfId="218" priority="423" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="244" priority="424" operator="equal">
+    <cfRule type="cellIs" dxfId="217" priority="427" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="216" priority="426" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="215" priority="425" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="214" priority="424" operator="equal">
       <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="243" priority="425" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="242" priority="426" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="241" priority="427" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:F54">
-    <cfRule type="cellIs" dxfId="240" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="213" priority="45" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="212" priority="46" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="211" priority="48" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="210" priority="43" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="239" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="209" priority="44" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="238" priority="45" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="237" priority="46" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="236" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="208" priority="47" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="235" priority="48" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:F65">
-    <cfRule type="cellIs" dxfId="234" priority="339" operator="equal">
+    <cfRule type="cellIs" dxfId="207" priority="339" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:F76">
-    <cfRule type="cellIs" dxfId="233" priority="173" operator="equal">
+    <cfRule type="cellIs" dxfId="206" priority="174" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="205" priority="176" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="204" priority="175" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="203" priority="173" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="232" priority="174" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="231" priority="175" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="230" priority="176" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="229" priority="177" operator="equal">
+    <cfRule type="cellIs" dxfId="202" priority="178" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="201" priority="177" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="228" priority="178" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:AH68">
-    <cfRule type="cellIs" dxfId="227" priority="245" operator="equal">
+    <cfRule type="cellIs" dxfId="200" priority="249" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="199" priority="248" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="198" priority="247" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="197" priority="246" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="196" priority="245" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="226" priority="246" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="225" priority="247" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="224" priority="248" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="223" priority="249" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47:F54">
-    <cfRule type="cellIs" dxfId="222" priority="375" operator="equal">
+    <cfRule type="cellIs" dxfId="195" priority="379" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="194" priority="380" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="193" priority="378" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="192" priority="377" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="191" priority="376" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="190" priority="375" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="221" priority="376" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="220" priority="377" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="219" priority="378" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="218" priority="379" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="217" priority="380" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:F65">
-    <cfRule type="cellIs" dxfId="216" priority="304" operator="equal">
+    <cfRule type="cellIs" dxfId="189" priority="309" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="188" priority="308" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="187" priority="307" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="306" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="185" priority="305" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="304" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="215" priority="305" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26:M43">
+    <cfRule type="cellIs" dxfId="183" priority="452" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="214" priority="306" operator="equal">
+    <cfRule type="cellIs" dxfId="182" priority="455" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="181" priority="454" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="456" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="179" priority="453" operator="equal">
       <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="307" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="212" priority="308" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="309" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I26:M34">
-    <cfRule type="cellIs" dxfId="210" priority="608" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="209" priority="609" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="610" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="611" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="206" priority="612" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27:M34">
-    <cfRule type="cellIs" dxfId="205" priority="607" operator="equal">
+    <cfRule type="cellIs" dxfId="178" priority="607" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I35:M43">
-    <cfRule type="cellIs" dxfId="204" priority="452" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="203" priority="453" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="454" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="455" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="200" priority="456" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I36:M43">
-    <cfRule type="cellIs" dxfId="199" priority="451" operator="equal">
+    <cfRule type="cellIs" dxfId="177" priority="451" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I46:M54">
-    <cfRule type="cellIs" dxfId="198" priority="417" operator="equal">
+    <cfRule type="cellIs" dxfId="176" priority="420" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="175" priority="419" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="418" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="173" priority="417" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="197" priority="418" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="419" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="420" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="194" priority="421" operator="equal">
+    <cfRule type="cellIs" dxfId="172" priority="421" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47:M54">
-    <cfRule type="cellIs" dxfId="193" priority="416" operator="equal">
+    <cfRule type="cellIs" dxfId="171" priority="416" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I57:M65">
-    <cfRule type="cellIs" dxfId="192" priority="334" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="337" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="169" priority="335" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="168" priority="334" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="191" priority="335" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="336" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="336" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="337" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="188" priority="338" operator="equal">
+    <cfRule type="cellIs" dxfId="166" priority="338" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I58:M65">
-    <cfRule type="cellIs" dxfId="187" priority="333" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="333" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I69:M76">
-    <cfRule type="cellIs" dxfId="186" priority="238" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="241" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="163" priority="240" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="239" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="161" priority="243" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="238" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="185" priority="239" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="242" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J50">
+    <cfRule type="cellIs" dxfId="158" priority="40" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="157" priority="39" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="156" priority="38" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="240" operator="equal">
+    <cfRule type="cellIs" dxfId="155" priority="41" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="154" priority="42" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="37" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J52">
+    <cfRule type="cellIs" dxfId="152" priority="32" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="151" priority="31" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="150" priority="36" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="149" priority="34" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="148" priority="35" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="147" priority="33" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="241" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L47:L48">
+    <cfRule type="cellIs" dxfId="146" priority="19" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="145" priority="22" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="182" priority="242" operator="equal">
+    <cfRule type="cellIs" dxfId="144" priority="20" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="143" priority="21" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="142" priority="24" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="23" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="243" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M49">
+    <cfRule type="cellIs" dxfId="140" priority="14" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="13" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="17" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="137" priority="16" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="18" operator="equal">
       <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="15" operator="equal">
+      <formula>"FÉRIAS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P36:Q43">
-    <cfRule type="cellIs" dxfId="180" priority="440" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="440" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="441" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="444" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="441" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="442" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="443" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="130" priority="442" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="443" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P54:Q54 P47:Q52">
+    <cfRule type="cellIs" dxfId="129" priority="409" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="128" priority="408" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="176" priority="444" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P47:Q52 P54:Q54">
-    <cfRule type="cellIs" dxfId="175" priority="405" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="405" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="406" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="406" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="407" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="407" operator="equal">
       <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="408" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="409" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P58:Q65">
-    <cfRule type="cellIs" dxfId="170" priority="322" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="325" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="326" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="122" priority="324" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="323" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="322" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="323" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P26:T43">
+    <cfRule type="cellIs" dxfId="119" priority="468" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="464" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="465" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="324" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="466" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="167" priority="325" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="467" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="326" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P26:T34">
-    <cfRule type="cellIs" dxfId="165" priority="524" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="525" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="526" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="527" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="528" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:T34">
-    <cfRule type="cellIs" dxfId="160" priority="523" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="523" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P35:T43">
-    <cfRule type="cellIs" dxfId="159" priority="464" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="465" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="466" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="467" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="468" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P36:T43">
-    <cfRule type="cellIs" dxfId="154" priority="463" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="463" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P46:T54">
-    <cfRule type="cellIs" dxfId="153" priority="132" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="132" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="133" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="133" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="134" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="134" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="135" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="135" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="136" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="136" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47:T54">
-    <cfRule type="cellIs" dxfId="148" priority="131" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="131" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P58:T65">
-    <cfRule type="cellIs" dxfId="147" priority="345" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="345" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P69:T76">
-    <cfRule type="cellIs" dxfId="146" priority="227" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="227" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="228" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="228" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="229" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="231" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="230" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="101" priority="229" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="230" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="250" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R48:R49">
+    <cfRule type="cellIs" dxfId="99" priority="1" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="2" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="3" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="4" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="95" priority="5" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="231" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="6" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="250" operator="equal">
-      <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47:W54">
-    <cfRule type="cellIs" dxfId="140" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="84" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="85" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="85" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="86" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="87" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="88" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W36:X36 W37:Y43">
-    <cfRule type="cellIs" dxfId="135" priority="499" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="499" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W26:AA34">
-    <cfRule type="cellIs" dxfId="134" priority="596" operator="equal">
+  <conditionalFormatting sqref="W26:AA35 W36:X36 W37:Y43">
+    <cfRule type="cellIs" dxfId="87" priority="500" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="597" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="501" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="598" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="502" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="599" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="503" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="600" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="504" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W27:AA34">
-    <cfRule type="cellIs" dxfId="129" priority="595" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="595" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W35:AA35 W36:X36 W37:Y43">
-    <cfRule type="cellIs" dxfId="128" priority="500" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="501" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="502" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="503" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="504" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W46:AA54">
-    <cfRule type="cellIs" dxfId="123" priority="126" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="126" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="127" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="127" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="128" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="128" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="129" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="129" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="130" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47:AA54">
-    <cfRule type="cellIs" dxfId="118" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="76" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57:AA65">
-    <cfRule type="cellIs" dxfId="117" priority="263" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="267" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="263" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="264" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="264" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="265" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="265" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="266" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="266" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="267" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W58:AA65">
-    <cfRule type="cellIs" dxfId="112" priority="262" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="262" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69:AA76">
-    <cfRule type="cellIs" dxfId="111" priority="209" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="211" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="68" priority="210" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="214" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="212" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="209" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="210" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="211" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="212" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="213" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="213" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="214" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y48:Y52">
-    <cfRule type="cellIs" dxfId="105" priority="434" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="439" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="434" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="435" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="435" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="436" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="436" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="437" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="437" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="438" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="438" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="439" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y59:Y65">
-    <cfRule type="cellIs" dxfId="99" priority="351" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="355" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="354" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="353" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="352" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="351" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="352" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="353" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="354" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="355" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="356" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="356" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y70:Y76">
-    <cfRule type="cellIs" dxfId="93" priority="256" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="261" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="256" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="257" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="257" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="258" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="258" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="259" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="259" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="260" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="260" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="261" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y36:AA43">
-    <cfRule type="cellIs" dxfId="87" priority="445" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="450" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="449" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="448" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="447" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="445" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="446" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="446" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="447" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="448" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="449" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="450" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z47:Z54">
-    <cfRule type="cellIs" dxfId="81" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="79" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="77" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="78" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="79" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="80" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="81" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="81" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD58:AE58 AD59:AF65">
-    <cfRule type="cellIs" dxfId="76" priority="316" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="317" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="318" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="319" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="320" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="321" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="316" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="317" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="318" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="319" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="320" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="321" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46:AH54">
-    <cfRule type="cellIs" dxfId="70" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="54" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="53" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="52" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="51" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="50" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="51" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="52" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="53" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="54" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD47:AH54">
-    <cfRule type="cellIs" dxfId="65" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="49" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD57:AH57 B57:F65 P57:T65">
-    <cfRule type="cellIs" dxfId="64" priority="340" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="344" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="343" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="342" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="341" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="340" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="341" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="342" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="343" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="344" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD69:AH76">
-    <cfRule type="cellIs" dxfId="59" priority="185" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="185" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="186" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="186" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="187" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="187" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="188" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="188" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="189" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="189" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="190" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="190" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF70:AF76">
-    <cfRule type="cellIs" dxfId="53" priority="203" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="207" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="208" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="203" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="204" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="204" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="205" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="205" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="206" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="206" operator="equal">
       <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="207" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="208" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF58:AH65">
-    <cfRule type="cellIs" dxfId="47" priority="310" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="311" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="310" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="311" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="312" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="312" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="313" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="313" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="314" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="314" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="315" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J50">
-    <cfRule type="cellIs" dxfId="41" priority="37" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="38" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="39" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="40" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="41" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="42" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J52">
-    <cfRule type="cellIs" dxfId="35" priority="31" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="32" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="33" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="34" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="35" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="36" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L48">
-    <cfRule type="cellIs" dxfId="29" priority="25" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="26" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="27" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="28" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="29" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="30" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L47">
-    <cfRule type="cellIs" dxfId="23" priority="19" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="23" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="24" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M49">
-    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="14" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="17" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="18" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R49">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="12" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R48">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="315" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8039,26 +7554,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C0248C8800EF904C9DD7E4C547A51745" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="99cce447bb6f5efd32e9ce5f489bef41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8" xmlns:ns3="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a9ec8dda6a39005fb0ea9e750809ba0" ns2:_="" ns3:_="">
     <xsd:import namespace="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8"/>
@@ -8299,26 +7794,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09527016-607A-4F07-A328-80E579B68BCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8"/>
-    <ds:schemaRef ds:uri="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27FD16DC-C657-454C-BC2E-356661B1CA7F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D068290E-986D-4310-B08B-7FF0E4AECC6B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8335,4 +7831,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27FD16DC-C657-454C-BC2E-356661B1CA7F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09527016-607A-4F07-A328-80E579B68BCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8"/>
+    <ds:schemaRef ds:uri="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Escala de Trabalho.xlsx
+++ b/Escala de Trabalho.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spotpromo.sharepoint.com/sites/bko.lbasaia/Documentos Compartilhados/PMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1104" documentId="8_{C9589A86-DEFA-4536-898C-3C99E4F500E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF43C6DE-7E1A-4FBB-BE34-F29F959D9FD9}"/>
+  <xr:revisionPtr revIDLastSave="1129" documentId="8_{C9589A86-DEFA-4536-898C-3C99E4F500E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5671E480-FEB9-41EA-9E68-891F1AF73258}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8597F27F-AEEC-4BA4-9237-ED3EB9E49D86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8597F27F-AEEC-4BA4-9237-ED3EB9E49D86}"/>
   </bookViews>
   <sheets>
-    <sheet name="agenda" sheetId="4" r:id="rId1"/>
+    <sheet name="AGENDA ESCRITORIO" sheetId="4" r:id="rId1"/>
+    <sheet name="FERIAS" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">agenda!$A$16:$A$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AGENDA ESCRITORIO'!$A$16:$A$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FERIAS!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="32">
   <si>
     <t>GUSTAVO</t>
   </si>
@@ -97,12 +99,54 @@
   <si>
     <t>ATESTADO</t>
   </si>
+  <si>
+    <t>Colaborador</t>
+  </si>
+  <si>
+    <t>Limite</t>
+  </si>
+  <si>
+    <t>Programação 1</t>
+  </si>
+  <si>
+    <t>Dias de Férias</t>
+  </si>
+  <si>
+    <t>RETORNO</t>
+  </si>
+  <si>
+    <t>VINICIUS DE ALMEIDA BONIFACIO ALVES</t>
+  </si>
+  <si>
+    <t>RODRIGO DELMONDES ARAUJO</t>
+  </si>
+  <si>
+    <t>EDFLANKLIN DANTAS DE MACEDO</t>
+  </si>
+  <si>
+    <t>DIOGO FABRICIO DA SILVA PESSOA</t>
+  </si>
+  <si>
+    <t>KIMBERLEY DA SILVA MIRANDA</t>
+  </si>
+  <si>
+    <t>GUSTAVO NEVES LAGROTTERIA</t>
+  </si>
+  <si>
+    <t>LILIAN BASAIA DA SILVA</t>
+  </si>
+  <si>
+    <t>EDNO OLIVEIRA ARAUJO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,8 +178,62 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,8 +264,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -190,11 +316,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -203,9 +357,47 @@
     <xf numFmtId="16" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="11" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="5">
+    <cellStyle name="Neutro" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Ruim" xfId="3" builtinId="27"/>
+    <cellStyle name="Título 1" xfId="2" builtinId="16"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="245">
     <dxf>
@@ -249,16 +441,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -276,6 +458,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -342,26 +554,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -407,6 +599,46 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -424,6 +656,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -439,36 +701,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -490,56 +722,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -606,11 +788,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -642,6 +844,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -678,36 +910,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -784,21 +986,31 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -820,31 +1032,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -926,16 +1128,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -946,11 +1138,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -972,11 +1164,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1058,16 +1260,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1322,31 +1514,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1474,6 +1666,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1529,6 +1731,36 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -1546,26 +1778,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1622,6 +1834,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1632,16 +1854,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1652,31 +1864,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1698,6 +1890,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1708,41 +1920,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1764,6 +1946,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1774,11 +1976,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1810,6 +2012,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1820,61 +2052,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1925,6 +2107,26 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -1942,6 +2144,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1957,36 +2189,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2008,41 +2210,51 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2074,6 +2286,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2084,31 +2326,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2130,6 +2352,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2145,76 +2407,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2245,6 +2437,36 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -2262,6 +2484,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2277,36 +2529,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2328,6 +2550,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2343,26 +2595,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2384,21 +2616,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2409,46 +2631,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2500,11 +2682,51 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2546,6 +2768,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2561,46 +2793,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2651,6 +2843,36 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -2668,6 +2890,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2678,6 +2920,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2688,61 +2960,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2764,72 +2986,52 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2851,41 +3053,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6694,56 +6886,56 @@
   </sheetData>
   <autoFilter ref="A16:A24" xr:uid="{FA93638E-3964-4B9F-B2A5-0DADAAE5D49F}"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="cellIs" dxfId="244" priority="628" operator="equal">
+    <cfRule type="cellIs" dxfId="244" priority="627" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="243" priority="628" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="243" priority="627" operator="equal">
-      <formula>"FOLGA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="242" priority="629" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:F12">
-    <cfRule type="cellIs" dxfId="241" priority="621" operator="equal">
+    <cfRule type="cellIs" dxfId="241" priority="620" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="240" priority="621" operator="equal">
       <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="240" priority="620" operator="equal">
-      <formula>"VIAGEM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="239" priority="75" operator="equal">
-      <formula>"CAMPO"</formula>
+    <cfRule type="cellIs" dxfId="239" priority="67" operator="equal">
+      <formula>"SPOT LESTE"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="238" priority="68" operator="equal">
       <formula>"PLATINA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="237" priority="67" operator="equal">
-      <formula>"SPOT LESTE"</formula>
+    <cfRule type="cellIs" dxfId="237" priority="75" operator="equal">
+      <formula>"CAMPO"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="236" priority="82" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B50">
-    <cfRule type="cellIs" dxfId="235" priority="74" operator="equal">
+    <cfRule type="cellIs" dxfId="235" priority="69" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="234" priority="70" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="233" priority="71" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="232" priority="72" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="231" priority="73" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="230" priority="74" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="234" priority="73" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="233" priority="72" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="232" priority="71" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="231" priority="70" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="230" priority="69" operator="equal">
-      <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47:E47">
@@ -6752,28 +6944,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F12">
-    <cfRule type="cellIs" dxfId="228" priority="623" operator="equal">
+    <cfRule type="cellIs" dxfId="228" priority="622" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="227" priority="623" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="227" priority="622" operator="equal">
-      <formula>"FOLGA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="226" priority="624" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:F43">
-    <cfRule type="cellIs" dxfId="225" priority="461" operator="equal">
+    <cfRule type="cellIs" dxfId="225" priority="458" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="224" priority="459" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="223" priority="460" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="222" priority="461" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="224" priority="460" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="223" priority="459" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="458" operator="equal">
-      <formula>"VIAGEM"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="221" priority="462" operator="equal">
       <formula>"SPOT"</formula>
@@ -6793,37 +6985,37 @@
     <cfRule type="cellIs" dxfId="218" priority="423" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="217" priority="427" operator="equal">
+    <cfRule type="cellIs" dxfId="217" priority="424" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="216" priority="425" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="215" priority="426" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="214" priority="427" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="216" priority="426" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="215" priority="425" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="214" priority="424" operator="equal">
-      <formula>"FÉRIAS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:F54">
-    <cfRule type="cellIs" dxfId="213" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="213" priority="43" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="212" priority="44" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="211" priority="45" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="212" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="210" priority="46" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="209" priority="47" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="208" priority="48" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="43" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="209" priority="44" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="47" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:F65">
@@ -6832,97 +7024,97 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:F76">
-    <cfRule type="cellIs" dxfId="206" priority="174" operator="equal">
+    <cfRule type="cellIs" dxfId="206" priority="173" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="205" priority="174" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="176" operator="equal">
-      <formula>"FOLGA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="204" priority="175" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="203" priority="173" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="178" operator="equal">
+    <cfRule type="cellIs" dxfId="203" priority="176" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="202" priority="177" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="201" priority="178" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="177" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:AH68">
-    <cfRule type="cellIs" dxfId="200" priority="249" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="248" operator="equal">
-      <formula>"HOME"</formula>
+    <cfRule type="cellIs" dxfId="200" priority="245" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="199" priority="246" operator="equal">
+      <formula>"FÉRIAS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="198" priority="247" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="197" priority="246" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="245" operator="equal">
-      <formula>"VIAGEM"</formula>
+    <cfRule type="cellIs" dxfId="197" priority="248" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="196" priority="249" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47:F54">
-    <cfRule type="cellIs" dxfId="195" priority="379" operator="equal">
+    <cfRule type="cellIs" dxfId="195" priority="375" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="194" priority="376" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="193" priority="377" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="192" priority="378" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="191" priority="379" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="194" priority="380" operator="equal">
+    <cfRule type="cellIs" dxfId="190" priority="380" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="378" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="377" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="191" priority="376" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="375" operator="equal">
-      <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:F65">
-    <cfRule type="cellIs" dxfId="189" priority="309" operator="equal">
+    <cfRule type="cellIs" dxfId="189" priority="304" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="188" priority="305" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="187" priority="306" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="307" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="185" priority="308" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="309" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="188" priority="308" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="307" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="306" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="185" priority="305" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="304" operator="equal">
-      <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:M43">
     <cfRule type="cellIs" dxfId="183" priority="452" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="182" priority="455" operator="equal">
-      <formula>"HOME"</formula>
+    <cfRule type="cellIs" dxfId="182" priority="453" operator="equal">
+      <formula>"FÉRIAS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="181" priority="454" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="456" operator="equal">
+    <cfRule type="cellIs" dxfId="180" priority="455" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="179" priority="456" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="453" operator="equal">
-      <formula>"FÉRIAS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27:M34">
@@ -6936,17 +7128,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I46:M54">
-    <cfRule type="cellIs" dxfId="176" priority="420" operator="equal">
+    <cfRule type="cellIs" dxfId="176" priority="417" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="175" priority="418" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="419" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="173" priority="420" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="419" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="418" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="417" operator="equal">
-      <formula>"VIAGEM"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="172" priority="421" operator="equal">
       <formula>"SPOT"</formula>
@@ -6958,17 +7150,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I57:M65">
-    <cfRule type="cellIs" dxfId="170" priority="337" operator="equal">
-      <formula>"HOME"</formula>
+    <cfRule type="cellIs" dxfId="170" priority="334" operator="equal">
+      <formula>"VIAGEM"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="169" priority="335" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="334" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="167" priority="336" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="336" operator="equal">
       <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="167" priority="337" operator="equal">
+      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="166" priority="338" operator="equal">
       <formula>"SPOT"</formula>
@@ -6980,54 +7172,54 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I69:M76">
-    <cfRule type="cellIs" dxfId="164" priority="241" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="238" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="163" priority="239" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="240" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="161" priority="241" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="240" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="239" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="243" operator="equal">
+    <cfRule type="cellIs" dxfId="160" priority="242" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="159" priority="243" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="238" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="242" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J50">
-    <cfRule type="cellIs" dxfId="158" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="37" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="157" priority="38" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="156" priority="39" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="155" priority="40" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="39" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="38" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="41" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="153" priority="42" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="37" operator="equal">
-      <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J52">
-    <cfRule type="cellIs" dxfId="152" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="152" priority="31" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="151" priority="32" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="31" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="36" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="150" priority="33" operator="equal">
+      <formula>"FÉRIAS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="149" priority="34" operator="equal">
       <formula>"FOLGA"</formula>
@@ -7035,116 +7227,116 @@
     <cfRule type="cellIs" dxfId="148" priority="35" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="33" operator="equal">
-      <formula>"FÉRIAS"</formula>
+    <cfRule type="cellIs" dxfId="147" priority="36" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L47:L48">
     <cfRule type="cellIs" dxfId="146" priority="19" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="145" priority="20" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="144" priority="21" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="143" priority="22" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="20" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="21" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="23" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="24" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="23" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49">
-    <cfRule type="cellIs" dxfId="140" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="13" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="14" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="13" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="17" operator="equal">
-      <formula>"HOME"</formula>
+    <cfRule type="cellIs" dxfId="138" priority="15" operator="equal">
+      <formula>"FÉRIAS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="137" priority="16" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="17" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="18" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="15" operator="equal">
-      <formula>"FÉRIAS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P36:Q43">
     <cfRule type="cellIs" dxfId="134" priority="440" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="444" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="441" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="441" operator="equal">
       <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="442" operator="equal">
+      <formula>"FOLGA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="131" priority="443" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="442" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="444" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P47:Q52 P54:Q54">
+    <cfRule type="cellIs" dxfId="129" priority="405" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="128" priority="406" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="407" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P54:Q54 P47:Q52">
-    <cfRule type="cellIs" dxfId="129" priority="409" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="408" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="125" priority="409" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="408" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="405" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="406" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="407" operator="equal">
-      <formula>"FOLGA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P58:Q65">
-    <cfRule type="cellIs" dxfId="124" priority="325" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="326" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="124" priority="322" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="323" operator="equal">
+      <formula>"FÉRIAS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="122" priority="324" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="323" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="322" operator="equal">
-      <formula>"VIAGEM"</formula>
+    <cfRule type="cellIs" dxfId="121" priority="325" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="326" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26:T43">
-    <cfRule type="cellIs" dxfId="119" priority="468" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="464" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="465" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="466" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="116" priority="467" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="468" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="464" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="465" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="466" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="467" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:T34">
@@ -7191,14 +7383,14 @@
     <cfRule type="cellIs" dxfId="104" priority="228" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="231" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="103" priority="229" operator="equal">
+      <formula>"FOLGA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="102" priority="230" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="229" operator="equal">
-      <formula>"FOLGA"</formula>
+    <cfRule type="cellIs" dxfId="101" priority="231" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="100" priority="250" operator="equal">
       <formula>"PLATINA 33B"</formula>
@@ -7291,20 +7483,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57:AA65">
-    <cfRule type="cellIs" dxfId="75" priority="267" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="263" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="264" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="265" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="266" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="267" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="263" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="264" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="265" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="266" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W58:AA65">
@@ -7313,114 +7505,114 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69:AA76">
-    <cfRule type="cellIs" dxfId="69" priority="211" operator="equal">
-      <formula>"FÉRIAS"</formula>
+    <cfRule type="cellIs" dxfId="69" priority="209" operator="equal">
+      <formula>"PLATINA 33B"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="68" priority="210" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="214" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="67" priority="211" operator="equal">
+      <formula>"FÉRIAS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="66" priority="212" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="209" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="213" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="213" operator="equal">
       <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="214" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y48:Y52">
-    <cfRule type="cellIs" dxfId="63" priority="439" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="434" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="435" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="436" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="437" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="59" priority="438" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="439" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="434" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="435" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="436" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="437" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="438" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y59:Y65">
-    <cfRule type="cellIs" dxfId="57" priority="355" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="354" operator="equal">
-      <formula>"FOLGA"</formula>
+    <cfRule type="cellIs" dxfId="57" priority="351" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="352" operator="equal">
+      <formula>"VIAGEM"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="55" priority="353" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="352" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="351" operator="equal">
-      <formula>"PLATINA 33B"</formula>
+    <cfRule type="cellIs" dxfId="54" priority="354" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="355" operator="equal">
+      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="52" priority="356" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y70:Y76">
-    <cfRule type="cellIs" dxfId="51" priority="261" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="256" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="257" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="258" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="259" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="260" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="261" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="256" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="257" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="258" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="259" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="260" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y36:AA43">
-    <cfRule type="cellIs" dxfId="45" priority="450" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="445" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="446" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="447" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="448" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="449" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="450" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="449" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="448" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="447" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="445" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="446" operator="equal">
-      <formula>"VIAGEM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z47:Z54">
-    <cfRule type="cellIs" dxfId="39" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="77" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="78" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="79" operator="equal">
       <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="77" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="78" operator="equal">
-      <formula>"FÉRIAS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="36" priority="80" operator="equal">
       <formula>"HOME"</formula>
@@ -7430,40 +7622,40 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD58:AE58 AD59:AF65">
-    <cfRule type="cellIs" dxfId="34" priority="317" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="316" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="317" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="318" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="318" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="319" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="319" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="320" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="320" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="321" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="321" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="316" operator="equal">
-      <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46:AH54">
-    <cfRule type="cellIs" dxfId="28" priority="54" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="53" operator="equal">
-      <formula>"HOME"</formula>
+    <cfRule type="cellIs" dxfId="28" priority="50" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="51" operator="equal">
+      <formula>"FÉRIAS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="26" priority="52" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="51" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="50" operator="equal">
-      <formula>"VIAGEM"</formula>
+    <cfRule type="cellIs" dxfId="25" priority="53" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="54" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD47:AH54">
@@ -7472,20 +7664,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD57:AH57 B57:F65 P57:T65">
-    <cfRule type="cellIs" dxfId="22" priority="344" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="343" operator="equal">
-      <formula>"HOME"</formula>
+    <cfRule type="cellIs" dxfId="22" priority="340" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="341" operator="equal">
+      <formula>"FÉRIAS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="20" priority="342" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="341" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="340" operator="equal">
-      <formula>"VIAGEM"</formula>
+    <cfRule type="cellIs" dxfId="19" priority="343" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="344" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD69:AH76">
@@ -7509,31 +7701,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF70:AF76">
-    <cfRule type="cellIs" dxfId="11" priority="207" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="203" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="204" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="205" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="206" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="207" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="208" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="208" operator="equal">
       <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="203" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="204" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="205" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="206" operator="equal">
-      <formula>"FOLGA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF58:AH65">
-    <cfRule type="cellIs" dxfId="5" priority="311" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="310" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="311" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="310" operator="equal">
-      <formula>"PLATINA 33B"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="3" priority="312" operator="equal">
       <formula>"FÉRIAS"</formula>
@@ -7553,7 +7745,262 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537AF333-CC02-40E4-ADE6-9A8EC00B9B52}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="14">
+        <v>46240</v>
+      </c>
+      <c r="C2" s="15">
+        <v>46076</v>
+      </c>
+      <c r="D2" s="16">
+        <v>8</v>
+      </c>
+      <c r="E2" s="15">
+        <f>C2+D2</f>
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="14">
+        <v>46380</v>
+      </c>
+      <c r="C3" s="17">
+        <v>46118</v>
+      </c>
+      <c r="D3" s="18">
+        <v>20</v>
+      </c>
+      <c r="E3" s="15">
+        <f>C3+D3</f>
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="14">
+        <v>46305</v>
+      </c>
+      <c r="C4" s="17">
+        <v>46146</v>
+      </c>
+      <c r="D4" s="18">
+        <v>20</v>
+      </c>
+      <c r="E4" s="15">
+        <f>C4+D4</f>
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="14">
+        <v>46427</v>
+      </c>
+      <c r="C5" s="17">
+        <v>46169</v>
+      </c>
+      <c r="D5" s="18">
+        <v>3</v>
+      </c>
+      <c r="E5" s="15">
+        <f>C5+D5</f>
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="14">
+        <v>46255</v>
+      </c>
+      <c r="C6" s="17">
+        <v>46195</v>
+      </c>
+      <c r="D6" s="18">
+        <v>15</v>
+      </c>
+      <c r="E6" s="15">
+        <f>C6+D6</f>
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="14">
+        <v>46467</v>
+      </c>
+      <c r="C7" s="17">
+        <v>46209</v>
+      </c>
+      <c r="D7" s="18">
+        <v>20</v>
+      </c>
+      <c r="E7" s="15">
+        <f>C7+D7</f>
+        <v>46229</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="14">
+        <v>46568</v>
+      </c>
+      <c r="C8" s="17">
+        <v>46237</v>
+      </c>
+      <c r="D8" s="18">
+        <v>20</v>
+      </c>
+      <c r="E8" s="15">
+        <f>C8+D8</f>
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="14">
+        <v>46427</v>
+      </c>
+      <c r="C9" s="17">
+        <v>46251</v>
+      </c>
+      <c r="D9" s="18">
+        <v>20</v>
+      </c>
+      <c r="E9" s="15">
+        <f>C9+D9</f>
+        <v>46271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="14">
+        <v>46380</v>
+      </c>
+      <c r="C10" s="19">
+        <v>46349</v>
+      </c>
+      <c r="D10" s="18">
+        <v>20</v>
+      </c>
+      <c r="E10" s="15">
+        <f>C10+D10</f>
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="14">
+        <v>46427</v>
+      </c>
+      <c r="C11" s="17">
+        <v>46358</v>
+      </c>
+      <c r="D11" s="18">
+        <v>10</v>
+      </c>
+      <c r="E11" s="15">
+        <f>C11+D11</f>
+        <v>46368</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="14">
+        <v>46240</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16">
+        <v>10</v>
+      </c>
+      <c r="E12" s="15">
+        <f>C12+D12</f>
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E12" xr:uid="{537AF333-CC02-40E4-ADE6-9A8EC00B9B52}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E12">
+      <sortCondition ref="C1:C12"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C0248C8800EF904C9DD7E4C547A51745" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="99cce447bb6f5efd32e9ce5f489bef41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8" xmlns:ns3="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a9ec8dda6a39005fb0ea9e750809ba0" ns2:_="" ns3:_="">
     <xsd:import namespace="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8"/>
@@ -7794,27 +8241,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09527016-607A-4F07-A328-80E579B68BCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8"/>
+    <ds:schemaRef ds:uri="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27FD16DC-C657-454C-BC2E-356661B1CA7F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D068290E-986D-4310-B08B-7FF0E4AECC6B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7831,23 +8277,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27FD16DC-C657-454C-BC2E-356661B1CA7F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09527016-607A-4F07-A328-80E579B68BCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8"/>
-    <ds:schemaRef ds:uri="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Escala de Trabalho.xlsx
+++ b/Escala de Trabalho.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spotpromo.sharepoint.com/sites/bko.lbasaia/Documentos Compartilhados/PMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1129" documentId="8_{C9589A86-DEFA-4536-898C-3C99E4F500E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5671E480-FEB9-41EA-9E68-891F1AF73258}"/>
+  <xr:revisionPtr revIDLastSave="1142" documentId="8_{C9589A86-DEFA-4536-898C-3C99E4F500E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39BDD658-F001-42B6-AA8A-C86FC8FF2973}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8597F27F-AEEC-4BA4-9237-ED3EB9E49D86}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8597F27F-AEEC-4BA4-9237-ED3EB9E49D86}"/>
   </bookViews>
   <sheets>
     <sheet name="AGENDA ESCRITORIO" sheetId="4" r:id="rId1"/>
@@ -402,6 +402,16 @@
   <dxfs count="245">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -417,16 +427,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -478,6 +478,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -534,41 +544,41 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -589,56 +599,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -656,6 +616,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -686,21 +676,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -722,11 +702,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -798,26 +788,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -844,6 +814,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -854,21 +844,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -910,6 +900,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -975,46 +985,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -1032,6 +1002,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1042,6 +1042,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1057,16 +1067,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1107,46 +1107,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -1164,6 +1124,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1174,6 +1154,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1194,6 +1184,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1204,11 +1204,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1249,46 +1249,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -1306,6 +1266,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1331,26 +1321,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1372,6 +1342,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1397,6 +1387,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1438,16 +1438,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1513,46 +1503,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -1570,6 +1520,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1590,6 +1550,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1600,31 +1580,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1646,6 +1616,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1671,36 +1661,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1722,41 +1682,41 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1834,6 +1794,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1849,6 +1819,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1890,6 +1880,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1900,31 +1930,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1956,16 +1966,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2098,6 +2098,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2108,21 +2128,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2230,26 +2240,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2286,6 +2276,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2296,6 +2296,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2311,26 +2331,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2381,36 +2381,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -2428,6 +2398,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2438,21 +2438,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2484,31 +2484,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2560,6 +2550,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2575,16 +2585,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2626,6 +2626,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2692,16 +2702,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2833,46 +2833,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF9C0006"/>
@@ -2890,6 +2850,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2920,6 +2900,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2940,16 +2930,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2960,11 +2940,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2986,6 +2966,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3002,6 +3002,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.59996337778862885"/>
@@ -3009,29 +3019,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3053,21 +3043,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4964,7 +4964,7 @@
         <v>10</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>11</v>
@@ -4973,7 +4973,7 @@
         <v>16</v>
       </c>
       <c r="Z47" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>9</v>
@@ -5044,7 +5044,7 @@
         <v>10</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>11</v>
@@ -5053,7 +5053,7 @@
         <v>16</v>
       </c>
       <c r="Z48" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>9</v>
@@ -5133,7 +5133,7 @@
         <v>16</v>
       </c>
       <c r="Z49" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>9</v>
@@ -5284,7 +5284,7 @@
         <v>10</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X51" s="3" t="s">
         <v>11</v>
@@ -5293,7 +5293,7 @@
         <v>16</v>
       </c>
       <c r="Z51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA51" s="3" t="s">
         <v>9</v>
@@ -5819,7 +5819,7 @@
         <v>0</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>9</v>
@@ -5828,7 +5828,7 @@
         <v>16</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>10</v>
@@ -5949,7 +5949,7 @@
         <v>4</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>9</v>
@@ -5958,7 +5958,7 @@
         <v>16</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>10</v>
@@ -6079,7 +6079,7 @@
         <v>2</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>9</v>
@@ -6088,7 +6088,7 @@
         <v>16</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>10</v>
@@ -6889,53 +6889,53 @@
     <cfRule type="cellIs" dxfId="244" priority="627" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="243" priority="628" operator="equal">
+    <cfRule type="cellIs" dxfId="243" priority="629" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="242" priority="628" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="242" priority="629" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:F12">
-    <cfRule type="cellIs" dxfId="241" priority="620" operator="equal">
+    <cfRule type="cellIs" dxfId="241" priority="621" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="240" priority="620" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="240" priority="621" operator="equal">
-      <formula>"FÉRIAS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="239" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="239" priority="82" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="238" priority="75" operator="equal">
+      <formula>"CAMPO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="237" priority="68" operator="equal">
+      <formula>"PLATINA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="236" priority="67" operator="equal">
       <formula>"SPOT LESTE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="238" priority="68" operator="equal">
-      <formula>"PLATINA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="237" priority="75" operator="equal">
-      <formula>"CAMPO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="236" priority="82" operator="equal">
-      <formula>"VIAGEM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B50">
-    <cfRule type="cellIs" dxfId="235" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="235" priority="74" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="234" priority="73" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="233" priority="72" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="232" priority="70" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="231" priority="69" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="234" priority="70" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="233" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="230" priority="71" operator="equal">
       <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="232" priority="72" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="231" priority="73" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="230" priority="74" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47:E47">
@@ -6944,31 +6944,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F12">
-    <cfRule type="cellIs" dxfId="228" priority="622" operator="equal">
-      <formula>"FOLGA"</formula>
+    <cfRule type="cellIs" dxfId="228" priority="624" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="227" priority="623" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="226" priority="624" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="226" priority="622" operator="equal">
+      <formula>"FOLGA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:F43">
-    <cfRule type="cellIs" dxfId="225" priority="458" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="224" priority="459" operator="equal">
-      <formula>"FÉRIAS"</formula>
+    <cfRule type="cellIs" dxfId="225" priority="461" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="224" priority="462" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="223" priority="460" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="461" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="221" priority="462" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="222" priority="459" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="221" priority="458" operator="equal">
+      <formula>"VIAGEM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:F34">
@@ -7024,65 +7024,65 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:F76">
-    <cfRule type="cellIs" dxfId="206" priority="173" operator="equal">
+    <cfRule type="cellIs" dxfId="206" priority="174" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="205" priority="175" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="204" priority="176" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="203" priority="177" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="202" priority="178" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="201" priority="173" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="174" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="175" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="203" priority="176" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="177" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="178" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:AH68">
     <cfRule type="cellIs" dxfId="200" priority="245" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="246" operator="equal">
+    <cfRule type="cellIs" dxfId="199" priority="247" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="198" priority="248" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="197" priority="249" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="196" priority="246" operator="equal">
       <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="247" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="197" priority="248" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="249" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47:F54">
-    <cfRule type="cellIs" dxfId="195" priority="375" operator="equal">
+    <cfRule type="cellIs" dxfId="195" priority="379" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="194" priority="375" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="194" priority="376" operator="equal">
+    <cfRule type="cellIs" dxfId="193" priority="376" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="377" operator="equal">
+    <cfRule type="cellIs" dxfId="192" priority="377" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="378" operator="equal">
+    <cfRule type="cellIs" dxfId="191" priority="378" operator="equal">
       <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="191" priority="379" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="190" priority="380" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:F65">
-    <cfRule type="cellIs" dxfId="189" priority="304" operator="equal">
-      <formula>"PLATINA 33B"</formula>
+    <cfRule type="cellIs" dxfId="189" priority="308" operator="equal">
+      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="188" priority="305" operator="equal">
       <formula>"VIAGEM"</formula>
@@ -7090,28 +7090,28 @@
     <cfRule type="cellIs" dxfId="187" priority="306" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="307" operator="equal">
+    <cfRule type="cellIs" dxfId="186" priority="309" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="185" priority="307" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="185" priority="308" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="309" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="184" priority="304" operator="equal">
+      <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:M43">
-    <cfRule type="cellIs" dxfId="183" priority="452" operator="equal">
+    <cfRule type="cellIs" dxfId="183" priority="455" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="182" priority="454" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="181" priority="453" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="452" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="182" priority="453" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="454" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="455" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="179" priority="456" operator="equal">
       <formula>"SPOT"</formula>
@@ -7131,17 +7131,17 @@
     <cfRule type="cellIs" dxfId="176" priority="417" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="418" operator="equal">
+    <cfRule type="cellIs" dxfId="175" priority="420" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="421" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="173" priority="419" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="172" priority="418" operator="equal">
       <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="419" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="420" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="421" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47:M54">
@@ -7150,17 +7150,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I57:M65">
-    <cfRule type="cellIs" dxfId="170" priority="334" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="337" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="169" priority="334" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="335" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="335" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="336" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="336" operator="equal">
       <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="167" priority="337" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="166" priority="338" operator="equal">
       <formula>"SPOT"</formula>
@@ -7172,43 +7172,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I69:M76">
-    <cfRule type="cellIs" dxfId="164" priority="238" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="239" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="163" priority="240" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="241" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="161" priority="242" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="243" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="159" priority="238" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="239" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="240" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="241" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="242" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="243" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J50">
-    <cfRule type="cellIs" dxfId="158" priority="37" operator="equal">
-      <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="38" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="39" operator="equal">
-      <formula>"FÉRIAS"</formula>
+    <cfRule type="cellIs" dxfId="157" priority="42" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="156" priority="41" operator="equal">
+      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="155" priority="40" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="41" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="42" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="154" priority="39" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="37" operator="equal">
+      <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J52">
@@ -7252,91 +7252,91 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49">
-    <cfRule type="cellIs" dxfId="140" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="14" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="13" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="14" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="18" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="137" priority="17" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="16" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="15" operator="equal">
       <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="16" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="17" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="18" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P36:Q43">
-    <cfRule type="cellIs" dxfId="134" priority="440" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="443" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="440" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="441" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="441" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="442" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="442" operator="equal">
       <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="443" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="130" priority="444" operator="equal">
       <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47:Q52 P54:Q54">
-    <cfRule type="cellIs" dxfId="129" priority="405" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="407" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="128" priority="408" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="409" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="126" priority="406" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="125" priority="405" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="406" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="407" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="408" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="409" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P58:Q65">
-    <cfRule type="cellIs" dxfId="124" priority="322" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="323" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="324" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="122" priority="325" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="326" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="322" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="323" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="324" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="325" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="326" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26:T43">
-    <cfRule type="cellIs" dxfId="119" priority="464" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="465" operator="equal">
-      <formula>"FÉRIAS"</formula>
+    <cfRule type="cellIs" dxfId="119" priority="468" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="467" operator="equal">
+      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="117" priority="466" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="467" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="468" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="116" priority="465" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="464" operator="equal">
+      <formula>"VIAGEM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:T34">
@@ -7350,20 +7350,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P46:T54">
-    <cfRule type="cellIs" dxfId="112" priority="132" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="136" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="134" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="110" priority="133" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="132" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="133" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="134" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="135" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="135" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="136" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47:T54">
@@ -7377,43 +7377,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P69:T76">
-    <cfRule type="cellIs" dxfId="105" priority="227" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="228" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="229" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="250" operator="equal">
+      <formula>"PLATINA 33B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="231" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="101" priority="230" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="227" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="228" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="229" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="230" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="231" operator="equal">
-      <formula>"SPOT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="250" operator="equal">
-      <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R48:R49">
-    <cfRule type="cellIs" dxfId="99" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="6" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="1" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="2" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="3" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="4" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="5" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="6" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47:W54">
@@ -7426,11 +7426,11 @@
     <cfRule type="cellIs" dxfId="91" priority="86" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="88" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="89" priority="87" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="88" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W36:X36 W37:Y43">
@@ -7439,20 +7439,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W26:AA35 W36:X36 W37:Y43">
-    <cfRule type="cellIs" dxfId="87" priority="500" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="504" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="86" priority="502" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="501" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="500" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="501" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="502" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="503" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="503" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="504" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W27:AA34">
@@ -7461,20 +7461,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W46:AA54">
-    <cfRule type="cellIs" dxfId="81" priority="126" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="127" operator="equal">
-      <formula>"FÉRIAS"</formula>
+    <cfRule type="cellIs" dxfId="81" priority="130" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="129" operator="equal">
+      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="79" priority="128" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="129" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="130" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="78" priority="127" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="77" priority="126" operator="equal">
+      <formula>"VIAGEM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47:AA54">
@@ -7489,14 +7489,14 @@
     <cfRule type="cellIs" dxfId="74" priority="264" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="265" operator="equal">
-      <formula>"FOLGA"</formula>
+    <cfRule type="cellIs" dxfId="73" priority="267" operator="equal">
+      <formula>"SPOT"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="72" priority="266" operator="equal">
       <formula>"HOME"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="267" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="71" priority="265" operator="equal">
+      <formula>"FOLGA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W58:AA65">
@@ -7508,20 +7508,20 @@
     <cfRule type="cellIs" dxfId="69" priority="209" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="210" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="211" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="214" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="213" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="212" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="210" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="211" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="212" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="213" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="214" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y48:Y52">
@@ -7534,65 +7534,65 @@
     <cfRule type="cellIs" dxfId="61" priority="436" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="437" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="438" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="59" priority="439" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="437" operator="equal">
       <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="438" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="439" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y59:Y65">
-    <cfRule type="cellIs" dxfId="57" priority="351" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="356" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="355" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="354" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="353" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="352" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="351" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="352" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="353" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="354" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="355" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="356" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y70:Y76">
-    <cfRule type="cellIs" dxfId="51" priority="256" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="257" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="258" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="259" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="260" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="261" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="256" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="257" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="258" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="259" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="260" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="261" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y36:AA43">
-    <cfRule type="cellIs" dxfId="45" priority="445" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="447" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="445" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="446" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="446" operator="equal">
       <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="447" operator="equal">
-      <formula>"FÉRIAS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="42" priority="448" operator="equal">
       <formula>"FOLGA"</formula>
@@ -7605,57 +7605,57 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z47:Z54">
-    <cfRule type="cellIs" dxfId="39" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="81" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="80" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="78" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="77" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="78" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="79" operator="equal">
       <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="80" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="81" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD58:AE58 AD59:AF65">
-    <cfRule type="cellIs" dxfId="34" priority="316" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="321" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="316" operator="equal">
       <formula>"PLATINA 33B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="317" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="317" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="318" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="318" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="319" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="319" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="320" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="320" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="321" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46:AH54">
-    <cfRule type="cellIs" dxfId="28" priority="50" operator="equal">
-      <formula>"VIAGEM"</formula>
+    <cfRule type="cellIs" dxfId="28" priority="52" operator="equal">
+      <formula>"FOLGA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="27" priority="51" operator="equal">
       <formula>"FÉRIAS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="52" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="50" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="54" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="53" operator="equal">
       <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="54" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD47:AH54">
@@ -7663,29 +7663,29 @@
       <formula>"PLATINA 33B"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD57:AH57 B57:F65 P57:T65">
-    <cfRule type="cellIs" dxfId="22" priority="340" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="341" operator="equal">
-      <formula>"FÉRIAS"</formula>
+  <conditionalFormatting sqref="AD57:AH57 P57:T65 B57:F65">
+    <cfRule type="cellIs" dxfId="22" priority="344" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="343" operator="equal">
+      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="20" priority="342" operator="equal">
       <formula>"FOLGA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="343" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="344" operator="equal">
-      <formula>"SPOT"</formula>
+    <cfRule type="cellIs" dxfId="19" priority="341" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="340" operator="equal">
+      <formula>"VIAGEM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD69:AH76">
-    <cfRule type="cellIs" dxfId="17" priority="185" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="186" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="185" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="186" operator="equal">
-      <formula>"VIAGEM"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="15" priority="187" operator="equal">
       <formula>"FÉRIAS"</formula>
@@ -7701,20 +7701,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF70:AF76">
-    <cfRule type="cellIs" dxfId="11" priority="203" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="204" operator="equal">
+      <formula>"VIAGEM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="205" operator="equal">
+      <formula>"FÉRIAS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="206" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="207" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="203" operator="equal">
       <formula>"PLATINA 33B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="204" operator="equal">
-      <formula>"VIAGEM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="205" operator="equal">
-      <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="206" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="207" operator="equal">
-      <formula>"HOME"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="6" priority="208" operator="equal">
       <formula>"SPOT"</formula>
@@ -7727,17 +7727,17 @@
     <cfRule type="cellIs" dxfId="4" priority="311" operator="equal">
       <formula>"VIAGEM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="312" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="313" operator="equal">
+      <formula>"FOLGA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="314" operator="equal">
+      <formula>"HOME"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="315" operator="equal">
+      <formula>"SPOT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="312" operator="equal">
       <formula>"FÉRIAS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="313" operator="equal">
-      <formula>"FOLGA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="314" operator="equal">
-      <formula>"HOME"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="315" operator="equal">
-      <formula>"SPOT"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -7788,7 +7788,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="15">
-        <f>C2+D2</f>
+        <f t="shared" ref="E2:E12" si="0">C2+D2</f>
         <v>46084</v>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
         <v>20</v>
       </c>
       <c r="E3" s="15">
-        <f>C3+D3</f>
+        <f t="shared" si="0"/>
         <v>46138</v>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="15">
-        <f>C4+D4</f>
+        <f t="shared" si="0"/>
         <v>46166</v>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="15">
-        <f>C5+D5</f>
+        <f t="shared" si="0"/>
         <v>46172</v>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="15">
-        <f>C6+D6</f>
+        <f t="shared" si="0"/>
         <v>46210</v>
       </c>
     </row>
@@ -7878,7 +7878,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="15">
-        <f>C7+D7</f>
+        <f t="shared" si="0"/>
         <v>46229</v>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="15">
-        <f>C8+D8</f>
+        <f t="shared" si="0"/>
         <v>46257</v>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="15">
-        <f>C9+D9</f>
+        <f t="shared" si="0"/>
         <v>46271</v>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="15">
-        <f>C10+D10</f>
+        <f t="shared" si="0"/>
         <v>46369</v>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="15">
-        <f>C11+D11</f>
+        <f t="shared" si="0"/>
         <v>46368</v>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="15">
-        <f>C12+D12</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -7981,26 +7981,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C0248C8800EF904C9DD7E4C547A51745" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="99cce447bb6f5efd32e9ce5f489bef41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8" xmlns:ns3="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a9ec8dda6a39005fb0ea9e750809ba0" ns2:_="" ns3:_="">
     <xsd:import namespace="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8"/>
@@ -8241,26 +8221,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09527016-607A-4F07-A328-80E579B68BCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8"/>
-    <ds:schemaRef ds:uri="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27FD16DC-C657-454C-BC2E-356661B1CA7F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D068290E-986D-4310-B08B-7FF0E4AECC6B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8277,4 +8258,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27FD16DC-C657-454C-BC2E-356661B1CA7F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09527016-607A-4F07-A328-80E579B68BCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e69c21a7-acf8-4fa1-a5df-4dc7c803cbc8"/>
+    <ds:schemaRef ds:uri="d337ff45-b2f2-4aee-a0da-7b5a3bfb7c3d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>